--- a/docs/testrail/spider_unity_cases.xlsx
+++ b/docs/testrail/spider_unity_cases.xlsx
@@ -190,6 +190,100 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">FL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Terms &amp; Conditions link opens the terms page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Delete Spider and reinstall it, or otherwise reset it so the Terms &amp; Conditions card is on screen. Do not tap Continue yet.
+2. Tap the Terms &amp; Conditions link.
+3. If Accept All Cookies appears, tap it and wait for the cookie banner to disappear.
+4. Close the page or tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The card shows links for Terms &amp; Conditions and Privacy Policy.
+2. A terms web page opens, not the Privacy Policy page.
+3. The banner is gone and the Terms of Service heading is fully visible.
+4. The Terms &amp; Conditions card is still there. Do not tap Continue yet.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Privacy Policy link opens the privacy page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the same Terms &amp; Conditions card, tap Privacy Policy.
+2. If Accept All Cookies appears, tap it and wait for the cookie banner to disappear.
+3. Close the page or tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. A privacy web page opens, not the Terms &amp; Conditions page.
+2. The banner is gone and the Privacy Notice heading is fully visible.
+3. The Terms &amp; Conditions card is still there. Continue is checked separately in FL-02.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">MM-01</t>
         </is>
       </c>
@@ -221,6 +315,48 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. Play, Stats, Options, Help, About, More Games, Choose Look, and the Spider logo are all on screen.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistics - Opens from the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From the main menu, tap Stats.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The Statistics screen opens. The header reads Statistics. The main menu is gone.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -276,6 +412,90 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">ST-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistics - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From Statistics, tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Options - Opens from the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Options</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From the main menu, tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The Options screen opens. The main menu is gone.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">OP-03</t>
         </is>
       </c>
@@ -492,6 +712,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">HP-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help - Opens on Introduction</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Help</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From the main menu, tap Help.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Help opens with the Introduction heading. The main menu is gone.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">HP-02</t>
         </is>
       </c>
@@ -536,6 +798,90 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">HP-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Help</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From Help, tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AB-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">About - Opens from the About menu item</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; About</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From the main menu, tap About.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The About screen opens. You can see the copyright line.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">AB-03</t>
         </is>
       </c>
@@ -777,6 +1123,48 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. FreeCell and Spiderette come into view. The back button and instruction line at the top stay put.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">MG-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Games - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; More Games</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From the More Games page, tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The main menu is showing.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -1667,6 +2055,48 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. It says Easy level, matching the game you started, not some other level.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victory - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Victory</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On Victory, tap the screen's own Back control — not New.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The main menu is showing. Leaving by Back leaves no game in progress.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3209,6 +3639,48 @@
         <is>
           <t xml:space="preserve">1. Game Center opens, headed Achievements.
 2. Last Score is showing again.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">LS-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last Score - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Last Score</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. From Last Score, tap Back until you reach the menu.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The main menu is showing.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -4029,6 +4501,300 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">FL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Terms &amp; Conditions link opens the terms page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delete Spider and reinstall it, or otherwise reset it so the Terms &amp; Conditions card is on screen. Do not tap Continue yet.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The card shows links for Terms &amp; Conditions and Privacy Policy.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Terms &amp; Conditions link opens the terms page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap the Terms &amp; Conditions link.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">A terms web page opens, not the Privacy Policy page.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Terms &amp; Conditions link opens the terms page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Accept All Cookies appears, tap it and wait for the cookie banner to disappear.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The banner is gone and the Terms of Service heading is fully visible.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Terms &amp; Conditions link opens the terms page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close the page or tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Terms &amp; Conditions card is still there. Do not tap Continue yet.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Privacy Policy link opens the privacy page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the same Terms &amp; Conditions card, tap Privacy Policy.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">A privacy web page opens, not the Terms &amp; Conditions page.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Privacy Policy link opens the privacy page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Accept All Cookies appears, tap it and wait for the cookie banner to disappear.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The banner is gone and the Privacy Notice heading is fully visible.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Privacy Policy link opens the privacy page</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close the page or tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Terms &amp; Conditions card is still there. Continue is checked separately in FL-02.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">MM-01</t>
         </is>
       </c>
@@ -4071,6 +4837,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">ST-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistics - Opens from the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the main menu, tap Stats.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Statistics screen opens. The header reads Statistics. The main menu is gone.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">ST-03</t>
         </is>
       </c>
@@ -4155,6 +4963,90 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">ST-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistics - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Statistics, tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Options - Opens from the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Options</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the main menu, tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Options screen opens. The main menu is gone.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">OP-03</t>
         </is>
       </c>
@@ -4491,6 +5383,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">HP-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help - Opens on Introduction</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Help</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the main menu, tap Help.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help opens with the Introduction heading. The main menu is gone.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">HP-02</t>
         </is>
       </c>
@@ -4575,6 +5509,90 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">HP-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Help</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Help, tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AB-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">About - Opens from the About menu item</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; About</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the main menu, tap About.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The About screen opens. You can see the copyright line.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">AB-03</t>
         </is>
       </c>
@@ -4827,6 +5845,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">MG-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Games - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; More Games</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the More Games page, tap Back.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">PL-01</t>
         </is>
       </c>
@@ -5877,6 +6937,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">VI-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victory - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Victory</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">On Victory, tap the screen's own Back control — not New.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main menu is showing. Leaving by Back leaves no game in progress.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">DL-01</t>
         </is>
       </c>
@@ -8008,6 +9110,48 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">Last Score is showing again.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">LS-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last Score - Back returns to the main menu</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Last Score</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Last Score, tap Back until you reach the menu.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main menu is showing.</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/docs/testrail/spider_unity_cases.xlsx
+++ b/docs/testrail/spider_unity_cases.xlsx
@@ -4072,6 +4072,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">HS-02</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Options - Contact Us still leaves Options without internet</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Options</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Turn Airplane Mode on and turn Wi-Fi off. Open Options and tap Contact Us.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. You leave Options. The support page may show a no-connection or failed-load screen instead of PeopleFun Support. That is the case — the redirect still happened.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">RL-01</t>
         </is>
       </c>
@@ -9583,6 +9625,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">HS-02</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Options - Contact Us still leaves Options without internet</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Options</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turn Airplane Mode on and turn Wi-Fi off. Open Options and tap Contact Us.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">You leave Options. The support page may show a no-connection or failed-load screen instead of PeopleFun Support. That is the case — the redirect still happened.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">RL-01</t>
         </is>
       </c>

--- a/docs/testrail/spider_unity_cases.xlsx
+++ b/docs/testrail/spider_unity_cases.xlsx
@@ -1302,6 +1302,50 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">PL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Play - Declining abandon stays on the picker</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Play</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. With a paused game, open Play and tap its difficulty again.
+2. Tap No.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. An abandon confirmation appears.
+2. The new deal is cancelled. The difficulty picker remains open, the game table has not started, and the paused game has not been discarded.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">QA-02</t>
         </is>
       </c>
@@ -2626,6 +2670,50 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">RS-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reset Statistics - Declining leaves scores alone</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destructive</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Stats, scroll to Reset Statistics, and tap it.
+2. Tap No.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. A reset confirmation appears.
+2. The confirmation closes, Statistics remains open, and the local scores are unchanged.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">CL-01</t>
         </is>
       </c>
@@ -3681,6 +3769,48 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AF-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad-free - No leaves you on About</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; App Store / Mail</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On About, tap ad free version and tap No on the confirmation.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The card closes. Spider stays in front on About and the App Store does not open.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -6055,6 +6185,90 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">PL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Play - Declining abandon stays on the picker</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Play</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">With a paused game, open Play and tap its difficulty again.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">An abandon confirmation appears.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">PL-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Play - Declining abandon stays on the picker</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Play</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap No.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The new deal is cancelled. The difficulty picker remains open, the game table has not started, and the paused game has not been discarded.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">QA-02</t>
         </is>
       </c>
@@ -7819,6 +8033,90 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">RS-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reset Statistics - Declining leaves scores alone</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destructive</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open Stats, scroll to Reset Statistics, and tap it.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">A reset confirmation appears.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">RS-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reset Statistics - Declining leaves scores alone</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Statistics</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destructive</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap No.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The confirmation closes, Statistics remains open, and the local scores are unchanged.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">CL-01</t>
         </is>
       </c>
@@ -9194,6 +9492,48 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">The main menu is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AF-01</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad-free - No leaves you on About</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; App Store / Mail</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">On About, tap ad free version and tap No on the confirmation.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The card closes. Spider stays in front on About and the App Store does not open.</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/docs/testrail/spider_unity_cases.xlsx
+++ b/docs/testrail/spider_unity_cases.xlsx
@@ -284,6 +284,52 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">FL-06</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Latest odd TestFlight build installs</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open TestFlight and tap Spider / Spider Solitaire.
+2. Scroll to Previous Builds and tap it. Tap the top row.
+3. If that page's version in parentheses is odd, delete Spider if it is installed, then tap Install and wait. If it is even, stop.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The TestFlight page for this game is showing.
+2. The newest build's page is showing.
+3. The odd build installs. An even newest build leaves the existing Spider installation unchanged.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">MM-01</t>
         </is>
       </c>
@@ -4967,6 +5013,132 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">FL-06</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Latest odd TestFlight build installs</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open TestFlight and tap Spider / Spider Solitaire.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The TestFlight page for this game is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-06</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Latest odd TestFlight build installs</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scroll to Previous Builds and tap it. Tap the top row.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The newest build's page is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">FL-06</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch - Latest odd TestFlight build installs</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Launch</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">If that page's version in parentheses is odd, delete Spider if it is installed, then tap Install and wait. If it is even, stop.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The odd build installs. An even newest build leaves the existing Spider installation unchanged.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">MM-01</t>
         </is>
       </c>

--- a/docs/testrail/spider_unity_cases.xlsx
+++ b/docs/testrail/spider_unity_cases.xlsx
@@ -310,15 +310,15 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open TestFlight and tap Spider / Spider Solitaire.
-2. Scroll to Previous Builds and tap it. Tap the top row.
-3. If that page's version in parentheses is odd, delete Spider if it is installed, then tap Install and wait. If it is even, stop.</t>
+2. Scroll to Previous Builds and tap it. Review all individual build rows.
+3. If an odd build exists, delete Spider if it is installed, then tap Install for that exact row and wait. If all builds are even, stop.</t>
         </is>
       </c>
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. The TestFlight page for this game is showing.
-2. The newest build's page is showing.
-3. The odd build installs. An even newest build leaves the existing Spider installation unchanged.</t>
+2. The greatest odd-numbered build is identified, regardless of where it appears in the list.
+3. The greatest odd build installs. An all-even list leaves the existing Spider installation unchanged.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3528,48 +3528,6 @@
     <row>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">TA-09</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ads - Starting a game after 30s on the menu shows an ad</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Functional</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Leave a table with Back after more than 30 seconds, close that ad onto the menu, stay on the menu more than 30 seconds, then resume or deal.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. An ad plays as you enter the game. This is the menu wait, not the same as the leave-game ad.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-    </row>
-    <row>
-      <c t="inlineStr">
-        <is>
           <t xml:space="preserve">TA-10</t>
         </is>
       </c>
@@ -3727,7 +3685,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Game Center opens, headed Leaderboards.
+          <t xml:space="preserve">1. Game Center opens, headed Leaderboards. If a notice card appears instead (scores may take a little time to upload), tap OK — Leaderboards opens from that, do not tap the link again.
 2. Last Score is showing again.</t>
         </is>
       </c>
@@ -3771,7 +3729,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Game Center opens, headed Achievements.
+          <t xml:space="preserve">1. Game Center opens, headed Achievements. If the same notice card appears, tap OK — Achievements opens from that, do not tap the link again.
 2. Last Score is showing again.</t>
         </is>
       </c>
@@ -5080,12 +5038,12 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Scroll to Previous Builds and tap it. Tap the top row.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">The newest build's page is showing.</t>
+          <t xml:space="preserve">Scroll to Previous Builds and tap it. Review all individual build rows.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The greatest odd-numbered build is identified, regardless of where it appears in the list.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -5122,12 +5080,12 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">If that page's version in parentheses is odd, delete Spider if it is installed, then tap Install and wait. If it is even, stop.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">The odd build installs. An even newest build leaves the existing Spider installation unchanged.</t>
+          <t xml:space="preserve">If an odd build exists, delete Spider if it is installed, then tap Install for that exact row and wait. If all builds are even, stop.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The greatest odd build installs. An all-even list leaves the existing Spider installation unchanged.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9297,12 +9255,12 @@
     <row>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">TA-09</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ads - Starting a game after 30s on the menu shows an ad</t>
+          <t xml:space="preserve">TA-10</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - Over 30s on the table, FAQ shows an ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9322,48 +9280,6 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Leave a table with Back after more than 30 seconds, close that ad onto the menu, stay on the menu more than 30 seconds, then resume or deal.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">An ad plays as you enter the game. This is the menu wait, not the same as the leave-game ad.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manual</t>
-        </is>
-      </c>
-    </row>
-    <row>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">TA-10</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ads - Over 30s on the table, FAQ shows an ad</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">Functional</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
           <t xml:space="preserve">Stay on the table more than 30 seconds. Open the in-game menu and tap FAQ.</t>
         </is>
       </c>
@@ -9495,7 +9411,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Game Center opens, headed Leaderboards.</t>
+          <t xml:space="preserve">Game Center opens, headed Leaderboards. If a notice card appears instead (scores may take a little time to upload), tap OK — Leaderboards opens from that, do not tap the link again.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9579,7 +9495,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Game Center opens, headed Achievements.</t>
+          <t xml:space="preserve">Game Center opens, headed Achievements. If the same notice card appears, tap OK — Achievements opens from that, do not tap the link again.</t>
         </is>
       </c>
       <c t="inlineStr">

--- a/docs/testrail/spider_unity_cases.xlsx
+++ b/docs/testrail/spider_unity_cases.xlsx
@@ -2198,6 +2198,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">VI-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victory - Score, time, moves and run rows all show data</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Victory</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the Victory screen, with Dev Panel closed, read the rows under current / rank / best.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. There are four rows, in the order the footer names them: scores, time, moves, run. Every row shows a value under current and a value or "-" under best. Score, time and moves also show a rank; run has no rank, as in the original game.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">DL-01</t>
         </is>
       </c>
@@ -2230,7 +2272,7 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. A Medium game is on the table.
-2. Victory appeared for Medium, then you can get back to the menu.</t>
+2. Victory appeared for Medium with all four rows (scores, time, moves, run) showing data, then you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2272,7 +2314,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Hard dealt a table, Victory appeared, and you can get back to the menu.</t>
+          <t xml:space="preserve">1. Hard dealt a table, Victory appeared with all four rows (scores, time, moves, run) showing data, and you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2314,7 +2356,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Bold dealt a table, Victory appeared, and you can get back to the menu.</t>
+          <t xml:space="preserve">1. Bold dealt a table, Victory appeared with all four rows (scores, time, moves, run) showing data, and you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -2356,7 +2398,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Expert dealt a table, Victory appeared, and you can get back to the menu.</t>
+          <t xml:space="preserve">1. Expert dealt a table, Victory appeared with all four rows (scores, time, moves, run) showing data, and you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3023,7 +3065,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Ads section shows the Live Network row</t>
+          <t xml:space="preserve">Ads - MAX Test Mode is on (fresh launch, restart after enabling it)</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3038,17 +3080,23 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. In the debugger, scroll until you can tap the Ads row. It reads Select Live Network when empty, or Live Network when a network is already chosen.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. That row is on screen and you can tap it.</t>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Start from a fresh launch: close Spider from the app switcher, open it again, unlock Dev Panel (About, tap the spider emblem five times quickly), tap Dev Panel, then Max Debugger. Scroll to the Ads section and read Test Mode Enabled. Do not trust a 'true' from an earlier session.
+2. Tap the blue Enable link on the Select Test Mode Network row.
+3. Tap OK. Close Spider from the app switcher and open it again.
+4. Unlock Dev Panel again (About, tap the spider emblem five times quickly), tap Dev Panel, then Max Debugger.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Test Mode Enabled says false. If it says true, tap Enable on the Select Live Network row, tap OK on Restart Required, and redo this step.
+2. A Restart Required pop-up asks you to re-launch the app.
+3. Spider opens. Dev Panel is hidden again.
+4. Test Mode Enabled now says true — Test Mode stayed on after the restart.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3065,7 +3113,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - AppLovin is the live network</t>
+          <t xml:space="preserve">Ads - Pangle is the Test Mode network</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3085,14 +3133,16 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tap the Live Network row. Wait for the picker (its title is Select Live Network). AppLovin also appears higher up under Completed SDK Integrations — ignore that one.
-2. If AppLovin is not already ticked, tap AppLovin.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The Select Live Network list is open.
-2. A checkmark sits on AppLovin.</t>
+          <t xml:space="preserve">1. Tap Select Test Mode Network. Wait for its own screen. Pangle also appears on the debugger page under Completed SDK Integrations — ignore that one.
+2. If Pangle is not already ticked, tap Pangle.
+3. Tap Back, then Done.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The Test Mode network list is open.
+2. A checkmark sits on Pangle.
+3. The debugger is closed. Test Mode stays on until Spider is relaunched again.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3109,7 +3159,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Leave-game ad: close the store X, then the ad X</t>
+          <t xml:space="preserve">Ads - Leave-game ad closes (double-arrow, then the X if shown)</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3130,13 +3180,13 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. Close the debugger (Done, then close Dev Panel). Start or resume a game. Wait about 30 seconds, then tap Back. If no ad appears, resume or deal again — that second enter is allowed.
-2. First tap the App Store product sheet's X (if that sheet appears). Then tap the ad's own circular X. Do not tap the skip arrows that move around.</t>
+2. About 5 seconds into the ad, a grey double-arrow circle appears top right (a short countdown shows there first). Tap it. If it opens an end card instead of closing, tap the end card's dark X, also top right.</t>
         </is>
       </c>
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. A full-screen ad plays inside Spider. You did not leave for another app.
-2. The store sheet closes first, then the ad.</t>
+2. The ad closes. No App Store sheet opens. If the ad shows no double-arrow and closes some other way, it came from a live network: fail this case and redo AD-03 and AD-04.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3173,7 +3223,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After both X buttons, wait for the game.</t>
+          <t xml:space="preserve">1. After the ad closes, wait for the game.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3215,7 +3265,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Start a game. Within about 8 seconds, open the in-game menu and tap Options. If an ad from an earlier session appears, close it, get back to the table, and try once more within 8 seconds.</t>
+          <t xml:space="preserve">1. With MAX in Test Mode on Pangle (AD-03, AD-04), start a game. Within about 8 seconds, open the in-game menu and tap Options. If an ad from an earlier session appears, close it, get back to the table, and try once more within 8 seconds.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3262,7 +3312,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. An ad plays. Close the store X, then the ad X.</t>
+          <t xml:space="preserve">1. An ad plays. Close it (double-arrow, then the X if an end card shows).</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3279,7 +3329,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Options within 30s of the Help ad has no ad</t>
+          <t xml:space="preserve">Ads - Options inside the Help ad's cooldown has no ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3299,12 +3349,14 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Right after you close the Help ad, go back to the table, open the in-game menu, and tap Options.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Options opens with no ad. The cooldown applies everywhere, not only on Victory.</t>
+          <t xml:space="preserve">1. Time the Help ad from the moment it appears until you close it. The cooldown is 30 seconds from when the ad APPEARED, so what is left after closing is 30 minus that time: closed after 10s leaves 20s, after 15s leaves 15s, after 30s or more leaves nothing (see TA-12).
+2. Inside that time left, go back to the table, open the in-game menu, and tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. You know how much cooldown is left.
+2. Options opens with no ad. The cooldown applies everywhere, not only on Victory.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3342,7 +3394,7 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. Stay on the table more than 30 seconds. Open Dev Panel and tap Complete Game.
-2. Close the store X, then the ad X, then close Dev Panel.</t>
+2. Close the ad (double-arrow, then the X if an end card shows), then close Dev Panel.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3365,7 +3417,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - New within 30s of the Victory ad has no ad</t>
+          <t xml:space="preserve">Ads - New inside the Victory ad's cooldown has no ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3385,12 +3437,14 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After closing the Victory ad, tap New within 30 seconds.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. A new table deals with no ad.</t>
+          <t xml:space="preserve">1. Time the Victory ad from the moment it appears until you close it. The time left is 30 seconds minus that — for example, closed after 15s leaves 15s.
+2. Close Dev Panel and tap New inside that time left.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. You know how much cooldown is left.
+2. A new table deals with no ad.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3407,7 +3461,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - New after 30s on Victory shows an ad</t>
+          <t xml:space="preserve">Ads - New after the Victory ad's cooldown runs out shows an ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3427,12 +3481,14 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Win again with Complete Game after more than 30 seconds on the table. Close that Victory ad, stay on Victory more than 30 seconds, then tap New.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. An ad plays before the next table. Close the store X, then the ad X.</t>
+          <t xml:space="preserve">1. Win again with Complete Game after more than 30 seconds on the table. Time that Victory ad from when it appears until you close it (double-arrow, then the X if an end card shows).
+2. Wait only the time left — 30 seconds minus the ad's time, plus a few seconds — then tap New. Closed after 20s means waiting about 10s, not 30s.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The Victory screen is visible.
+2. An ad plays before the next table. Close it (double-arrow, then the X if an end card shows).</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3474,7 +3530,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. An ad plays. After the store X and the ad X, you are on the main menu — not the table.</t>
+          <t xml:space="preserve">1. An ad plays. After you close it, you are on the main menu — not the table.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3491,7 +3547,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Starting a game within 30s on the menu has no ad</t>
+          <t xml:space="preserve">Ads - Starting a game right after the Back ad has no ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3511,12 +3567,12 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After the Back ad closed onto the menu, wait under 30 seconds and resume or deal a game.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The table appears with no ad.</t>
+          <t xml:space="preserve">1. After the Back ad closed onto the menu, straight away — inside the time left (30 seconds minus the ad's time) — resume or deal a game.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The table appears with no ad. Resume never shows an ad.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -3559,6 +3615,142 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">1. An ad plays. After it closes you can get back to the table.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-11</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Victory ad up 30s or more, New shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Stay on the table more than 30 seconds. Open Dev Panel and tap Complete Game.
+2. Leave the ad up at least 35 seconds from when it appeared — do not tap its double-arrow or X before then. Then close it and Dev Panel.
+3. Tap New straight away.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Victory appears with an ad on top.
+2. The Victory screen is visible.
+3. Another ad plays before the next table. An ad up 30s or more leaves no cooldown.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-12</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Help ad up 30s or more, Options shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Stay on the table more than 30 seconds. Open the in-game menu and tap Help.
+2. Leave the ad up at least 35 seconds from when it appeared. Then close it (double-arrow, then the X if an end card shows) and go back to the table.
+3. Straight away, open the in-game menu and tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. An ad plays.
+2. The game table is showing.
+3. Another ad plays, even though you were on the table only a few seconds.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-13</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - Options after the Help ad's cooldown runs out shows an ad</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. After TA-03 (Options with no ad), go back to the table.
+2. Wait until the Help ad's cooldown has run out — 30 seconds from when that ad APPEARED, plus a few seconds — then open the in-game menu and tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The game table is showing.
+2. An ad plays, sooner than 30 seconds after the Help ad was closed.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -7365,6 +7557,48 @@
     <row>
       <c t="inlineStr">
         <is>
+          <t xml:space="preserve">VI-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victory - Score, time, moves and run rows all show data</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Victory</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">On the Victory screen, with Dev Panel closed, read the rows under current / rank / best.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">There are four rows, in the order the footer names them: scores, time, moves, run. Every row shows a value under current and a value or "-" under best. Score, time and moves also show a rank; run has no rank, as in the original game.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
           <t xml:space="preserve">DL-01</t>
         </is>
       </c>
@@ -7437,7 +7671,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Victory appeared for Medium, then you can get back to the menu.</t>
+          <t xml:space="preserve">Victory appeared for Medium with all four rows (scores, time, moves, run) showing data, then you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -7479,7 +7713,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Hard dealt a table, Victory appeared, and you can get back to the menu.</t>
+          <t xml:space="preserve">Hard dealt a table, Victory appeared with all four rows (scores, time, moves, run) showing data, and you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -7521,7 +7755,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Bold dealt a table, Victory appeared, and you can get back to the menu.</t>
+          <t xml:space="preserve">Bold dealt a table, Victory appeared with all four rows (scores, time, moves, run) showing data, and you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -7563,7 +7797,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Expert dealt a table, Victory appeared, and you can get back to the menu.</t>
+          <t xml:space="preserve">Expert dealt a table, Victory appeared with all four rows (scores, time, moves, run) showing data, and you can get back to the menu.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8630,7 +8864,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Ads section shows the Live Network row</t>
+          <t xml:space="preserve">Ads - MAX Test Mode is on (fresh launch, restart after enabling it)</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8645,17 +8879,143 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">In the debugger, scroll until you can tap the Ads row. It reads Select Live Network when empty, or Live Network when a network is already chosen.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">That row is on screen and you can tap it.</t>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start from a fresh launch: close Spider from the app switcher, open it again, unlock Dev Panel (About, tap the spider emblem five times quickly), tap Dev Panel, then Max Debugger. Scroll to the Ads section and read Test Mode Enabled. Do not trust a 'true' from an earlier session.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Mode Enabled says false. If it says true, tap Enable on the Select Live Network row, tap OK on Restart Required, and redo this step.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - MAX Test Mode is on (fresh launch, restart after enabling it)</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap the blue Enable link on the Select Test Mode Network row.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Restart Required pop-up asks you to re-launch the app.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - MAX Test Mode is on (fresh launch, restart after enabling it)</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap OK. Close Spider from the app switcher and open it again.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider opens. Dev Panel is hidden again.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - MAX Test Mode is on (fresh launch, restart after enabling it)</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unlock Dev Panel again (About, tap the spider emblem five times quickly), tap Dev Panel, then Max Debugger.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Mode Enabled now says true — Test Mode stayed on after the restart.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8672,7 +9032,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - AppLovin is the live network</t>
+          <t xml:space="preserve">Ads - Pangle is the Test Mode network</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8692,12 +9052,12 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Tap the Live Network row. Wait for the picker (its title is Select Live Network). AppLovin also appears higher up under Completed SDK Integrations — ignore that one.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Select Live Network list is open.</t>
+          <t xml:space="preserve">Tap Select Test Mode Network. Wait for its own screen. Pangle also appears on the debugger page under Completed SDK Integrations — ignore that one.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Test Mode network list is open.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8714,7 +9074,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - AppLovin is the live network</t>
+          <t xml:space="preserve">Ads - Pangle is the Test Mode network</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8734,12 +9094,54 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">If AppLovin is not already ticked, tap AppLovin.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">A checkmark sits on AppLovin.</t>
+          <t xml:space="preserve">If Pangle is not already ticked, tap Pangle.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">A checkmark sits on Pangle.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD-04</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - Pangle is the Test Mode network</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap Back, then Done.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The debugger is closed. Test Mode stays on until Spider is relaunched again.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8756,7 +9158,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Leave-game ad: close the store X, then the ad X</t>
+          <t xml:space="preserve">Ads - Leave-game ad closes (double-arrow, then the X if shown)</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8798,7 +9200,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Leave-game ad: close the store X, then the ad X</t>
+          <t xml:space="preserve">Ads - Leave-game ad closes (double-arrow, then the X if shown)</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8818,12 +9220,12 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">First tap the App Store product sheet's X (if that sheet appears). Then tap the ad's own circular X. Do not tap the skip arrows that move around.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">The store sheet closes first, then the ad.</t>
+          <t xml:space="preserve">About 5 seconds into the ad, a grey double-arrow circle appears top right (a short countdown shows there first). Tap it. If it opens an end card instead of closing, tap the end card's dark X, also top right.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ad closes. No App Store sheet opens. If the ad shows no double-arrow and closes some other way, it came from a live network: fail this case and redo AD-03 and AD-04.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8860,7 +9262,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">After both X buttons, wait for the game.</t>
+          <t xml:space="preserve">After the ad closes, wait for the game.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8902,7 +9304,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Start a game. Within about 8 seconds, open the in-game menu and tap Options. If an ad from an earlier session appears, close it, get back to the table, and try once more within 8 seconds.</t>
+          <t xml:space="preserve">With MAX in Test Mode on Pangle (AD-03, AD-04), start a game. Within about 8 seconds, open the in-game menu and tap Options. If an ad from an earlier session appears, close it, get back to the table, and try once more within 8 seconds.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8949,7 +9351,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">An ad plays. Close the store X, then the ad X.</t>
+          <t xml:space="preserve">An ad plays. Close it (double-arrow, then the X if an end card shows).</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8966,7 +9368,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Options within 30s of the Help ad has no ad</t>
+          <t xml:space="preserve">Ads - Options inside the Help ad's cooldown has no ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -8986,7 +9388,49 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Right after you close the Help ad, go back to the table, open the in-game menu, and tap Options.</t>
+          <t xml:space="preserve">Time the Help ad from the moment it appears until you close it. The cooldown is 30 seconds from when the ad APPEARED, so what is left after closing is 30 minus that time: closed after 10s leaves 20s, after 15s leaves 15s, after 30s or more leaves nothing (see TA-12).</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">You know how much cooldown is left.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-03</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - Options inside the Help ad's cooldown has no ad</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inside that time left, go back to the table, open the in-game menu, and tap Options.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9070,7 +9514,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Close the store X, then the ad X, then close Dev Panel.</t>
+          <t xml:space="preserve">Close the ad (double-arrow, then the X if an end card shows), then close Dev Panel.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9092,7 +9536,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - New within 30s of the Victory ad has no ad</t>
+          <t xml:space="preserve">Ads - New inside the Victory ad's cooldown has no ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9112,7 +9556,49 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">After closing the Victory ad, tap New within 30 seconds.</t>
+          <t xml:space="preserve">Time the Victory ad from the moment it appears until you close it. The time left is 30 seconds minus that — for example, closed after 15s leaves 15s.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">You know how much cooldown is left.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-05</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - New inside the Victory ad's cooldown has no ad</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close Dev Panel and tap New inside that time left.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9134,7 +9620,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - New after 30s on Victory shows an ad</t>
+          <t xml:space="preserve">Ads - New after the Victory ad's cooldown runs out shows an ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9154,12 +9640,54 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Win again with Complete Game after more than 30 seconds on the table. Close that Victory ad, stay on Victory more than 30 seconds, then tap New.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">An ad plays before the next table. Close the store X, then the ad X.</t>
+          <t xml:space="preserve">Win again with Complete Game after more than 30 seconds on the table. Time that Victory ad from when it appears until you close it (double-arrow, then the X if an end card shows).</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Victory screen is visible.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-06</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - New after the Victory ad's cooldown runs out shows an ad</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wait only the time left — 30 seconds minus the ad's time, plus a few seconds — then tap New. Closed after 20s means waiting about 10s, not 30s.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">An ad plays before the next table. Close it (double-arrow, then the X if an end card shows).</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9201,7 +9729,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">An ad plays. After the store X and the ad X, you are on the main menu — not the table.</t>
+          <t xml:space="preserve">An ad plays. After you close it, you are on the main menu — not the table.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9218,7 +9746,7 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">Ads - Starting a game within 30s on the menu has no ad</t>
+          <t xml:space="preserve">Ads - Starting a game right after the Back ad has no ad</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9238,12 +9766,12 @@
       </c>
       <c t="inlineStr">
         <is>
-          <t xml:space="preserve">After the Back ad closed onto the menu, wait under 30 seconds and resume or deal a game.</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t xml:space="preserve">The table appears with no ad.</t>
+          <t xml:space="preserve">After the Back ad closed onto the menu, straight away — inside the time left (30 seconds minus the ad's time) — resume or deal a game.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The table appears with no ad. Resume never shows an ad.</t>
         </is>
       </c>
       <c t="inlineStr">
@@ -9286,6 +9814,342 @@
       <c t="inlineStr">
         <is>
           <t xml:space="preserve">An ad plays. After it closes you can get back to the table.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-11</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Victory ad up 30s or more, New shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stay on the table more than 30 seconds. Open Dev Panel and tap Complete Game.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victory appears with an ad on top.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-11</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Victory ad up 30s or more, New shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leave the ad up at least 35 seconds from when it appeared — do not tap its double-arrow or X before then. Then close it and Dev Panel.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Victory screen is visible.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-11</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Victory ad up 30s or more, New shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tap New straight away.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Another ad plays before the next table. An ad up 30s or more leaves no cooldown.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-12</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Help ad up 30s or more, Options shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stay on the table more than 30 seconds. Open the in-game menu and tap Help.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">An ad plays.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-12</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Help ad up 30s or more, Options shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leave the ad up at least 35 seconds from when it appeared. Then close it (double-arrow, then the X if an end card shows) and go back to the table.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The game table is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-12</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - After a Help ad up 30s or more, Options shows an ad at once</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Straight away, open the in-game menu and tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Another ad plays, even though you were on the table only a few seconds.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-13</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - Options after the Help ad's cooldown runs out shows an ad</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">After TA-03 (Options with no ad), go back to the table.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">The game table is showing.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA-13</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads - Options after the Help ad's cooldown runs out shows an ad</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Solitaire Unity &gt; Ads</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functional</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wait until the Help ad's cooldown has run out — 30 seconds from when that ad APPEARED, plus a few seconds — then open the in-game menu and tap Options.</t>
+        </is>
+      </c>
+      <c t="inlineStr">
+        <is>
+          <t xml:space="preserve">An ad plays, sooner than 30 seconds after the Help ad was closed.</t>
         </is>
       </c>
       <c t="inlineStr">
